--- a/www/flightdata/xlsx/eoss-360.xlsx
+++ b/www/flightdata/xlsx/eoss-360.xlsx
@@ -4584,7 +4584,7 @@
         <v>30473.9</v>
       </c>
       <c r="I2">
-        <v>947</v>
+        <v>627</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
